--- a/03_Outputs/all/01_TablasDescriptivas/idx15_vejez.xlsx
+++ b/03_Outputs/all/01_TablasDescriptivas/idx15_vejez.xlsx
@@ -399,7 +399,7 @@
         <v>13.84046740794182</v>
       </c>
       <c r="D2">
-        <v>9.397678572549912</v>
+        <v>9.397678572549911</v>
       </c>
       <c r="E2">
         <v>0.4273585379123688</v>
@@ -421,7 +421,7 @@
         <v>8.691129318714141</v>
       </c>
       <c r="D3">
-        <v>6.047865181183779</v>
+        <v>6.047865181183777</v>
       </c>
       <c r="E3">
         <v>0.6311079859733582</v>
@@ -465,7 +465,7 @@
         <v>-26.9609905009297</v>
       </c>
       <c r="D5">
-        <v>7.293118435307086</v>
+        <v>7.293118435307087</v>
       </c>
       <c r="E5">
         <v>-42.0365535248042</v>
@@ -509,7 +509,7 @@
         <v>-30.17174634087624</v>
       </c>
       <c r="D7">
-        <v>8.137723159085414</v>
+        <v>8.137723159085416</v>
       </c>
       <c r="E7">
         <v>-45.4353338968724</v>
@@ -553,7 +553,7 @@
         <v>-32.66836989813005</v>
       </c>
       <c r="D9">
-        <v>8.642167794652126</v>
+        <v>8.642167794652124</v>
       </c>
       <c r="E9">
         <v>-47.513389441469</v>

--- a/03_Outputs/all/01_TablasDescriptivas/idx15_vejez.xlsx
+++ b/03_Outputs/all/01_TablasDescriptivas/idx15_vejez.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -499,67 +499,23 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Índice envejecimiento (urb.)</t>
+          <t>Mortalidad IAM x100k</t>
         </is>
       </c>
       <c r="B7">
         <v>125</v>
       </c>
       <c r="C7">
-        <v>-30.17174634087624</v>
+        <v>-75.26264</v>
       </c>
       <c r="D7">
-        <v>8.137723159085416</v>
+        <v>25.01897428804399</v>
       </c>
       <c r="E7">
-        <v>-45.4353338968724</v>
+        <v>-146.61</v>
       </c>
       <c r="F7">
-        <v>-12.8676470588235</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Índice envejecimiento H (urb.)</t>
-        </is>
-      </c>
-      <c r="B8">
-        <v>125</v>
-      </c>
-      <c r="C8">
-        <v>-27.38278762520513</v>
-      </c>
-      <c r="D8">
-        <v>7.707765425792005</v>
-      </c>
-      <c r="E8">
-        <v>-42.8706326723324</v>
-      </c>
-      <c r="F8">
-        <v>-12.4705882352941</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Índice envejecimiento M (urb.)</t>
-        </is>
-      </c>
-      <c r="B9">
-        <v>125</v>
-      </c>
-      <c r="C9">
-        <v>-32.66836989813005</v>
-      </c>
-      <c r="D9">
-        <v>8.642167794652124</v>
-      </c>
-      <c r="E9">
-        <v>-47.513389441469</v>
-      </c>
-      <c r="F9">
-        <v>-13.2992327365729</v>
+        <v>-8.619999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/03_Outputs/all/01_TablasDescriptivas/idx15_vejez.xlsx
+++ b/03_Outputs/all/01_TablasDescriptivas/idx15_vejez.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -499,22 +499,110 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>Índice envejecimiento (urb.)</t>
+        </is>
+      </c>
+      <c r="B7">
+        <v>125</v>
+      </c>
+      <c r="C7">
+        <v>-30.17174634087624</v>
+      </c>
+      <c r="D7">
+        <v>8.137723159085416</v>
+      </c>
+      <c r="E7">
+        <v>-45.4353338968724</v>
+      </c>
+      <c r="F7">
+        <v>-12.8676470588235</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Índice envejecimiento (urb.)</t>
+        </is>
+      </c>
+      <c r="B8">
+        <v>125</v>
+      </c>
+      <c r="C8">
+        <v>-30.17174634087624</v>
+      </c>
+      <c r="D8">
+        <v>8.137723159085416</v>
+      </c>
+      <c r="E8">
+        <v>-45.4353338968724</v>
+      </c>
+      <c r="F8">
+        <v>-12.8676470588235</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Índice envejecimiento (rural)</t>
+        </is>
+      </c>
+      <c r="B9">
+        <v>125</v>
+      </c>
+      <c r="C9">
+        <v>-25.94478688104298</v>
+      </c>
+      <c r="D9">
+        <v>7.895185095935003</v>
+      </c>
+      <c r="E9">
+        <v>-42.0487401900041</v>
+      </c>
+      <c r="F9">
+        <v>-5.91780821917808</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Índice envejecimiento H (rural)</t>
+        </is>
+      </c>
+      <c r="B10">
+        <v>125</v>
+      </c>
+      <c r="C10">
+        <v>-26.55089345740436</v>
+      </c>
+      <c r="D10">
+        <v>7.570143619160206</v>
+      </c>
+      <c r="E10">
+        <v>-42.2972972972973</v>
+      </c>
+      <c r="F10">
+        <v>-5.66844919786096</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>Mortalidad IAM x100k</t>
         </is>
       </c>
-      <c r="B7">
-        <v>125</v>
-      </c>
-      <c r="C7">
+      <c r="B11">
+        <v>125</v>
+      </c>
+      <c r="C11">
         <v>-75.26264</v>
       </c>
-      <c r="D7">
+      <c r="D11">
         <v>25.01897428804399</v>
       </c>
-      <c r="E7">
+      <c r="E11">
         <v>-146.61</v>
       </c>
-      <c r="F7">
+      <c r="F11">
         <v>-8.619999999999999</v>
       </c>
     </row>
